--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-04-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-04-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,25 +476,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Planet Insulation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Online</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Insulation Shop</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Insulation Bee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Trade Insulations</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Materials Market</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Insulation Wholesale</t>
         </is>
@@ -548,25 +558,35 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>£12.35</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>£16.75</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>£24.78</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>£14.75</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>£13.04</t>
         </is>
@@ -620,25 +640,35 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£15.03</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>£19.50</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>£28.72</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>£17.37</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>£16.13</t>
         </is>
@@ -692,25 +722,35 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£18.11</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>£22.78</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>£31.91</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>£21.93</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>£18.80</t>
         </is>
@@ -764,25 +804,35 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>£19.41</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>£24.35</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>£37.78</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>£22.78</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>£19.69</t>
         </is>
@@ -836,25 +886,35 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£24.27</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>£29.63</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>£43.78</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>£28.29</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>£25.35</t>
         </is>
@@ -908,25 +968,35 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>£27.38</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>£35.00</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>£48.11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>£31.73</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>£26.98</t>
         </is>
@@ -980,25 +1050,35 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>£26.57</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>£34.82</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>£52.17</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>£31.77</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>£28.44</t>
         </is>
@@ -1052,25 +1132,35 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>£30.95</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>£38.53</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>£45.88</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>£36.05</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>£30.92</t>
         </is>
@@ -1124,25 +1214,35 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£33.38</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>£41.35</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>£53.74</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>£39.70</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>£35.29</t>
         </is>
@@ -1196,25 +1296,35 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>£32.94</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>£42.14</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>£54.67</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>£39.07</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>£33.89</t>
         </is>
@@ -1268,25 +1378,35 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>£51.19</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>£58.55</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>£47.47</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>£41.12</t>
         </is>
@@ -1340,25 +1460,35 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£41.65</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>£49.01</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>£64.44</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>£48.04</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>£42.12</t>
         </is>
@@ -1412,25 +1542,35 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>£47.31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>£59.35</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>£64.87</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>£57.26</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>£48.64</t>
         </is>
@@ -1484,25 +1624,35 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£51.05</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>£60.38</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>£73.44</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>£60.41</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>£44.90</t>
         </is>
@@ -1556,25 +1706,35 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£50.08</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>£75.21</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>£76.10</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>£58.05</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Add to Enquiry</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>£50.38</t>
         </is>
